--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/MISSISSIPPI_2016.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/MISSISSIPPI_2016.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D661"/>
+  <dimension ref="A1:D655"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C4">
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C5">
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -505,10 +535,15 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Acapetahua</t>
@@ -623,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C19">
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -684,10 +769,15 @@
         <v>2</v>
       </c>
       <c r="D23">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -701,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chiapa de Corzo</t>
+          <t>Chiapa De Corzo</t>
         </is>
       </c>
       <c r="C25">
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Chicomuselo</t>
@@ -727,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C27">
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Copainalá</t>
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Francisco León</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -827,10 +967,15 @@
         <v>2</v>
       </c>
       <c r="D34">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>La Grandeza</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -883,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -896,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -922,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Ostuacán</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -957,10 +1147,15 @@
         <v>2</v>
       </c>
       <c r="D44">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Pichucalco</t>
@@ -974,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -987,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Pueblo Nuevo Solistahuacán</t>
@@ -996,10 +1201,15 @@
         <v>2</v>
       </c>
       <c r="D47">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Reforma</t>
@@ -1009,10 +1219,15 @@
         <v>2</v>
       </c>
       <c r="D48">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Sabanilla</t>
@@ -1026,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salto de Agua</t>
+          <t>Salto De Agua</t>
         </is>
       </c>
       <c r="C50">
@@ -1039,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C51">
@@ -1052,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -1065,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Socoltenango</t>
@@ -1078,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Solosuchiapa</t>
@@ -1091,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -1104,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Sunuapa</t>
@@ -1117,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -1130,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -1143,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -1156,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -1169,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Tumbalá</t>
@@ -1182,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -1191,10 +1471,15 @@
         <v>2</v>
       </c>
       <c r="D62">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1208,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -1221,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -1230,10 +1525,15 @@
         <v>2</v>
       </c>
       <c r="D65">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Villaflores</t>
@@ -1247,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1278,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Carichí</t>
@@ -1291,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -1304,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1317,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -1326,10 +1651,15 @@
         <v>2</v>
       </c>
       <c r="D72">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -1343,19 +1673,29 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C74">
         <v>2</v>
       </c>
       <c r="D74">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1369,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -1378,13 +1723,18 @@
         <v>2</v>
       </c>
       <c r="D76">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>San Francisco de Borja</t>
+          <t>San Francisco De Borja</t>
         </is>
       </c>
       <c r="C77">
@@ -1395,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1426,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -1439,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Cuatro Ciénegas</t>
@@ -1452,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -1465,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>General Cepeda</t>
@@ -1478,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -1491,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Monclova</t>
@@ -1504,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1517,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Parras</t>
@@ -1530,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -1539,10 +1939,15 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Saltillo</t>
@@ -1556,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>San Juan de Sabinas</t>
+          <t>San Juan De Sabinas</t>
         </is>
       </c>
       <c r="C90">
@@ -1569,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1582,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1613,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1626,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1635,13 +2065,13 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1657,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1670,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1683,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1696,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1709,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1722,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1735,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1748,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1761,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -1774,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1783,10 +2263,15 @@
         <v>2</v>
       </c>
       <c r="D106">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1800,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1831,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1844,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Nazas</t>
@@ -1857,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nombre de Dios</t>
+          <t>Nombre De Dios</t>
         </is>
       </c>
       <c r="C112">
@@ -1870,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Santiago Papasquiaro</t>
@@ -1883,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1898,12 +2413,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C115">
@@ -1914,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C116">
@@ -1927,19 +2447,29 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Amanalco</t>
@@ -1953,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -1966,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1979,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -1988,23 +2533,33 @@
         <v>2</v>
       </c>
       <c r="D121">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -2018,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C124">
@@ -2031,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Jaltenco</t>
@@ -2044,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Jiquipilco</t>
@@ -2053,10 +2623,15 @@
         <v>2</v>
       </c>
       <c r="D126">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -2070,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -2083,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C129">
@@ -2096,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -2109,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Otumba</t>
@@ -2122,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C132">
@@ -2135,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Soyaniquilpan de Juárez</t>
+          <t>Soyaniquilpan De Juárez</t>
         </is>
       </c>
       <c r="C133">
@@ -2148,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -2161,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -2174,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -2187,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -2196,10 +2821,15 @@
         <v>2</v>
       </c>
       <c r="D137">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -2213,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -2226,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C140">
@@ -2239,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -2248,10 +2893,15 @@
         <v>2</v>
       </c>
       <c r="D141">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Tianguistenco</t>
@@ -2265,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C143">
@@ -2278,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -2291,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2304,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Tultepec</t>
@@ -2317,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Villa de Allende</t>
+          <t>Villa De Allende</t>
         </is>
       </c>
       <c r="C147">
@@ -2330,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -2339,10 +3019,15 @@
         <v>2</v>
       </c>
       <c r="D148">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Zumpahuacán</t>
@@ -2352,10 +3037,15 @@
         <v>2</v>
       </c>
       <c r="D149">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2383,10 +3073,15 @@
         <v>2</v>
       </c>
       <c r="D151">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Acámbaro</t>
@@ -2400,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>San Miguel de Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C153">
@@ -2413,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C154">
@@ -2426,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C155">
@@ -2439,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Atarjea</t>
@@ -2452,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -2465,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -2478,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Coroneo</t>
@@ -2491,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -2500,10 +3235,15 @@
         <v>2</v>
       </c>
       <c r="D160">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -2517,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -2526,13 +3271,18 @@
         <v>2</v>
       </c>
       <c r="D162">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C163">
@@ -2543,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -2556,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -2569,19 +3329,29 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Jaral del Progreso</t>
+          <t>Jaral Del Progreso</t>
         </is>
       </c>
       <c r="C166">
         <v>2</v>
       </c>
       <c r="D166">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -2595,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>León</t>
@@ -2608,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -2621,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -2634,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -2643,13 +3433,18 @@
         <v>2</v>
       </c>
       <c r="D171">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Purísima del Rincón</t>
+          <t>Purísima Del Rincón</t>
         </is>
       </c>
       <c r="C172">
@@ -2660,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -2673,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -2682,13 +3487,18 @@
         <v>2</v>
       </c>
       <c r="D174">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>San Diego de la Unión</t>
+          <t>San Diego De La Unión</t>
         </is>
       </c>
       <c r="C175">
@@ -2699,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -2712,9 +3527,14 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C177">
@@ -2725,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -2734,13 +3559,18 @@
         <v>2</v>
       </c>
       <c r="D178">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C179">
@@ -2751,9 +3581,14 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C180">
@@ -2764,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -2777,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -2790,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C183">
@@ -2803,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -2816,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Xichú</t>
@@ -2829,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2849,7 +3714,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C187">
@@ -2860,9 +3725,14 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C188">
@@ -2873,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Apaxtla</t>
@@ -2886,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -2899,9 +3779,14 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C191">
@@ -2912,19 +3797,29 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C192">
         <v>2</v>
       </c>
       <c r="D192">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -2938,9 +3833,14 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Buenavista de Cuéllar</t>
+          <t>Buenavista De Cuéllar</t>
         </is>
       </c>
       <c r="C194">
@@ -2951,22 +3851,32 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C195">
         <v>2</v>
       </c>
       <c r="D195">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C196">
@@ -2977,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -2990,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -3003,9 +3923,14 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C199">
@@ -3016,19 +3941,29 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C200">
         <v>2</v>
       </c>
       <c r="D200">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -3038,10 +3973,15 @@
         <v>2</v>
       </c>
       <c r="D201">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -3055,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C203">
@@ -3068,32 +4013,47 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C204">
         <v>2</v>
       </c>
       <c r="D204">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>La Unión de Isidoro Montes de Oca</t>
+          <t>La Unión De Isidoro Montes De Oca</t>
         </is>
       </c>
       <c r="C205">
         <v>2</v>
       </c>
       <c r="D205">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -3107,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -3120,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -3133,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -3146,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -3159,9 +4139,14 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C211">
@@ -3172,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -3181,23 +4171,33 @@
         <v>2</v>
       </c>
       <c r="D212">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C213">
         <v>2</v>
       </c>
       <c r="D213">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -3211,9 +4211,14 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Tixtla de Guerrero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C215">
@@ -3224,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Tlacoapa</t>
@@ -3237,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -3250,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Xochistlahuaca</t>
@@ -3259,10 +4279,15 @@
         <v>2</v>
       </c>
       <c r="D218">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Zapotitlán Tablas</t>
@@ -3276,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -3289,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Zitlala</t>
@@ -3302,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3333,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -3346,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Alfajayucan</t>
@@ -3359,9 +4409,14 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Atotonilco de Tula</t>
+          <t>Atotonilco De Tula</t>
         </is>
       </c>
       <c r="C226">
@@ -3372,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Calnali</t>
@@ -3385,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Cardonal</t>
@@ -3398,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -3411,19 +4481,29 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C230">
         <v>2</v>
       </c>
       <c r="D230">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -3437,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -3450,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Huautla</t>
@@ -3463,19 +4553,29 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Huejutla de Reyes</t>
+          <t>Huejutla De Reyes</t>
         </is>
       </c>
       <c r="C234">
         <v>2</v>
       </c>
       <c r="D234">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -3485,10 +4585,15 @@
         <v>2</v>
       </c>
       <c r="D235">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -3502,19 +4607,29 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Jacala de Ledezma</t>
+          <t>Jacala De Ledezma</t>
         </is>
       </c>
       <c r="C237">
         <v>2</v>
       </c>
       <c r="D237">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>La Misión</t>
@@ -3528,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -3541,9 +4661,14 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Molango de Escamilla</t>
+          <t>Molango De Escamilla</t>
         </is>
       </c>
       <c r="C240">
@@ -3554,9 +4679,14 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C241">
@@ -3567,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Pacula</t>
@@ -3576,10 +4711,15 @@
         <v>2</v>
       </c>
       <c r="D242">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Pisaflores</t>
@@ -3593,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>San Bartolo Tutotepec</t>
@@ -3606,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>San Salvador</t>
@@ -3619,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Tasquillo</t>
@@ -3632,9 +4787,14 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Tenango de Doria</t>
+          <t>Tenango De Doria</t>
         </is>
       </c>
       <c r="C247">
@@ -3645,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Tepeapulco</t>
@@ -3658,9 +4823,14 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerrero</t>
+          <t>Tepehuacán De Guerrero</t>
         </is>
       </c>
       <c r="C249">
@@ -3671,9 +4841,14 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Tepeji del Río de Ocampo</t>
+          <t>Tepeji Del Río De Ocampo</t>
         </is>
       </c>
       <c r="C250">
@@ -3684,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Tetepango</t>
@@ -3697,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Tianguistengo</t>
@@ -3710,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Tlanchinol</t>
@@ -3723,9 +4913,14 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C254">
@@ -3736,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Xochicoatlán</t>
@@ -3749,19 +4949,29 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Zacualtipán de Ángeles</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C256">
         <v>2</v>
       </c>
       <c r="D256">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -3775,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3802,10 +5017,15 @@
         <v>2</v>
       </c>
       <c r="D259">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Atengo</t>
@@ -3819,9 +5039,14 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C261">
@@ -3832,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Bolaños</t>
@@ -3845,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Cabo Corrientes</t>
@@ -3858,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -3871,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Ejutla</t>
@@ -3884,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>El Grullo</t>
@@ -3897,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>El Limón</t>
@@ -3910,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -3923,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -3936,9 +5201,14 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Jilotlán de los Dolores</t>
+          <t>Jilotlán De Los Dolores</t>
         </is>
       </c>
       <c r="C270">
@@ -3949,9 +5219,14 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C271">
@@ -3962,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -3971,10 +5251,15 @@
         <v>2</v>
       </c>
       <c r="D272">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -3988,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -4001,9 +5291,14 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>San Juanito de Escobedo</t>
+          <t>San Juanito De Escobedo</t>
         </is>
       </c>
       <c r="C275">
@@ -4014,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -4027,9 +5327,14 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C277">
@@ -4040,9 +5345,14 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C278">
@@ -4053,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -4066,9 +5381,14 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C280">
@@ -4079,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -4092,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -4101,13 +5431,18 @@
         <v>2</v>
       </c>
       <c r="D282">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Zacoalco de Torres</t>
+          <t>Zacoalco De Torres</t>
         </is>
       </c>
       <c r="C283">
@@ -4118,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -4127,10 +5467,15 @@
         <v>2</v>
       </c>
       <c r="D284">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -4140,10 +5485,15 @@
         <v>2</v>
       </c>
       <c r="D285">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4175,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -4188,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Aporo</t>
@@ -4201,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -4210,10 +5575,15 @@
         <v>2</v>
       </c>
       <c r="D290">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Chavinda</t>
@@ -4227,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Epitacio Huerta</t>
@@ -4240,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -4253,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -4266,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Ixtlán</t>
@@ -4279,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -4292,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -4301,10 +5701,15 @@
         <v>2</v>
       </c>
       <c r="D297">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -4318,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -4327,10 +5737,15 @@
         <v>2</v>
       </c>
       <c r="D299">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -4344,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -4357,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -4370,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -4383,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Parácuaro</t>
@@ -4396,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Peribán</t>
@@ -4409,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -4422,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -4435,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -4444,10 +5899,15 @@
         <v>2</v>
       </c>
       <c r="D308">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Senguio</t>
@@ -4461,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Tlalpujahua</t>
@@ -4474,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Tumbiscatío</t>
@@ -4483,10 +5953,15 @@
         <v>2</v>
       </c>
       <c r="D311">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -4500,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -4513,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -4522,10 +6007,15 @@
         <v>2</v>
       </c>
       <c r="D314">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Tzitzio</t>
@@ -4535,10 +6025,15 @@
         <v>2</v>
       </c>
       <c r="D315">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -4552,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Vista Hermosa</t>
@@ -4565,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -4578,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -4591,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -4604,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -4617,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4648,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -4661,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Miacatlán</t>
@@ -4674,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -4687,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Tetecala</t>
@@ -4700,9 +6245,14 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C328">
@@ -4713,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Yecapixtla</t>
@@ -4726,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Zacatepec</t>
@@ -4739,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4770,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -4779,10 +6349,15 @@
         <v>2</v>
       </c>
       <c r="D333">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -4792,10 +6367,15 @@
         <v>2</v>
       </c>
       <c r="D334">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4827,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Cadereyta Jiménez</t>
@@ -4840,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Doctor Arroyo</t>
@@ -4849,10 +6439,15 @@
         <v>2</v>
       </c>
       <c r="D338">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Galeana</t>
@@ -4866,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -4875,10 +6475,15 @@
         <v>2</v>
       </c>
       <c r="D340">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Linares</t>
@@ -4892,19 +6497,29 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Mier y Noriega</t>
+          <t>Mier Y Noriega</t>
         </is>
       </c>
       <c r="C342">
         <v>2</v>
       </c>
       <c r="D342">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Montemorelos</t>
@@ -4918,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -4931,19 +6551,29 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C345">
         <v>2</v>
       </c>
       <c r="D345">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>San Pedro Garza García</t>
@@ -4957,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4977,7 +6612,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C348">
@@ -4988,19 +6623,29 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Coicoyán de las Flores</t>
+          <t>Coicoyán De Las Flores</t>
         </is>
       </c>
       <c r="C349">
         <v>2</v>
       </c>
       <c r="D349">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -5014,35 +6659,50 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C351">
         <v>2</v>
       </c>
       <c r="D351">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Tlaxiaco</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C352">
         <v>2</v>
       </c>
       <c r="D352">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C353">
@@ -5053,9 +6713,14 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C354">
@@ -5066,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -5075,10 +6745,15 @@
         <v>2</v>
       </c>
       <c r="D355">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -5088,13 +6763,18 @@
         <v>2</v>
       </c>
       <c r="D356">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C357">
@@ -5105,45 +6785,65 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C358">
         <v>2</v>
       </c>
       <c r="D358">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C359">
         <v>2</v>
       </c>
       <c r="D359">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>San Felipe Jalapa de Díaz</t>
+          <t>San Felipe Jalapa De Díaz</t>
         </is>
       </c>
       <c r="C360">
         <v>2</v>
       </c>
       <c r="D360">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>San Felipe Usila</t>
@@ -5153,10 +6853,15 @@
         <v>2</v>
       </c>
       <c r="D361">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
           <t>San Ildefonso Villa Alta</t>
@@ -5170,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -5179,10 +6889,15 @@
         <v>2</v>
       </c>
       <c r="D363">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>San Juan Bautista Valle Nacional</t>
@@ -5196,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>San Juan Cotzocón</t>
@@ -5209,6 +6929,11 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>San Juan Guichicovi</t>
@@ -5218,10 +6943,15 @@
         <v>2</v>
       </c>
       <c r="D366">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
           <t>San Juan Ñumí</t>
@@ -5235,6 +6965,11 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
           <t>San Lucas Zoquiápam</t>
@@ -5248,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -5257,13 +6997,18 @@
         <v>2</v>
       </c>
       <c r="D369">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>San Miguel del Puerto</t>
+          <t>San Miguel Del Puerto</t>
         </is>
       </c>
       <c r="C370">
@@ -5274,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>San Miguel Ejutla</t>
@@ -5287,6 +7037,11 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
           <t>San Miguel Panixtlahuaca</t>
@@ -5300,6 +7055,11 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
           <t>San Pablo Tijaltepec</t>
@@ -5313,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>San Pedro Teutila</t>
@@ -5326,6 +7091,11 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
           <t>San Pedro Yaneri</t>
@@ -5339,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>San Sebastián Tecomaxtlahuaca</t>
@@ -5348,10 +7123,15 @@
         <v>2</v>
       </c>
       <c r="D376">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -5365,6 +7145,11 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
           <t>Santa Catarina Tayata</t>
@@ -5378,6 +7163,11 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
           <t>Santa Cruz Itundujia</t>
@@ -5391,6 +7181,11 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -5400,13 +7195,18 @@
         <v>2</v>
       </c>
       <c r="D380">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Santa Inés de Zaragoza</t>
+          <t>Santa Inés De Zaragoza</t>
         </is>
       </c>
       <c r="C381">
@@ -5417,9 +7217,14 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Santa Inés del Monte</t>
+          <t>Santa Inés Del Monte</t>
         </is>
       </c>
       <c r="C382">
@@ -5430,6 +7235,11 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>Santa Lucía Miahuatlán</t>
@@ -5443,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>Santa María Colotepec</t>
@@ -5452,10 +7267,15 @@
         <v>2</v>
       </c>
       <c r="D384">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>Santa María Ipalapa</t>
@@ -5469,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -5478,10 +7303,15 @@
         <v>2</v>
       </c>
       <c r="D386">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>Santa María Pápalo</t>
@@ -5495,6 +7325,11 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>Santa María Tecomavaca</t>
@@ -5508,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>Santa María Temaxcaltepec</t>
@@ -5521,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>Santa María Zacatepec</t>
@@ -5530,10 +7375,15 @@
         <v>2</v>
       </c>
       <c r="D390">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -5547,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -5560,6 +7415,11 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -5573,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Santiago Tetepec</t>
@@ -5586,6 +7451,11 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
           <t>Santiago Yaitepec</t>
@@ -5595,10 +7465,15 @@
         <v>2</v>
       </c>
       <c r="D395">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Santo Domingo Armenta</t>
@@ -5612,6 +7487,11 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
           <t>Santo Domingo Petapa</t>
@@ -5625,6 +7505,11 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>Santo Domingo Tehuantepec</t>
@@ -5638,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -5651,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>Santos Reyes Pápalo</t>
@@ -5664,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -5673,13 +7573,18 @@
         <v>2</v>
       </c>
       <c r="D401">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Tamazulápam del Espíritu Santo</t>
+          <t>Tamazulápam Del Espíritu Santo</t>
         </is>
       </c>
       <c r="C402">
@@ -5690,9 +7595,14 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C403">
@@ -5703,9 +7613,14 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Villa de Etla</t>
+          <t>Villa De Etla</t>
         </is>
       </c>
       <c r="C404">
@@ -5716,22 +7631,32 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Villa de Tututepec</t>
+          <t>Villa De Tututepec</t>
         </is>
       </c>
       <c r="C405">
         <v>2</v>
       </c>
       <c r="D405">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Villa Sola de Vega</t>
+          <t>Villa Sola De Vega</t>
         </is>
       </c>
       <c r="C406">
@@ -5742,19 +7667,29 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C407">
         <v>2</v>
       </c>
       <c r="D407">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5786,6 +7721,11 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>Acateno</t>
@@ -5799,6 +7739,11 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -5812,6 +7757,11 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>Ajalpan</t>
@@ -5825,6 +7775,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -5838,6 +7793,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>Atzitzihuacán</t>
@@ -5851,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>Chapulco</t>
@@ -5860,10 +7825,15 @@
         <v>2</v>
       </c>
       <c r="D415">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -5873,13 +7843,18 @@
         <v>2</v>
       </c>
       <c r="D416">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C417">
@@ -5890,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Cuyoaco</t>
@@ -5899,10 +7879,15 @@
         <v>2</v>
       </c>
       <c r="D418">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>Honey</t>
@@ -5916,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -5929,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Huatlatlauca</t>
@@ -5942,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -5951,10 +7951,15 @@
         <v>2</v>
       </c>
       <c r="D422">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>Huitziltepec</t>
@@ -5968,9 +7973,14 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C424">
@@ -5981,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Jalpan</t>
@@ -5994,9 +8009,14 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C426">
@@ -6007,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>Pahuatlán</t>
@@ -6020,19 +8045,29 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C428">
         <v>2</v>
       </c>
       <c r="D428">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -6046,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -6059,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>San Gabriel Chilac</t>
@@ -6072,6 +8117,11 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -6085,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -6094,10 +8149,15 @@
         <v>2</v>
       </c>
       <c r="D433">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -6111,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Tlacuilotepec</t>
@@ -6124,6 +8189,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -6137,6 +8207,11 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -6150,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>Xochiltepec</t>
@@ -6163,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -6176,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6196,7 +8286,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C441">
@@ -6207,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Arroyo Seco</t>
@@ -6220,9 +8315,14 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C443">
@@ -6233,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Corregidora</t>
@@ -6246,6 +8351,11 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -6259,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Huimilpan</t>
@@ -6268,13 +8383,18 @@
         <v>2</v>
       </c>
       <c r="D446">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C447">
@@ -6285,9 +8405,14 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C448">
@@ -6298,19 +8423,29 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C449">
         <v>2</v>
       </c>
       <c r="D449">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -6324,6 +8459,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
           <t>San Joaquín</t>
@@ -6337,9 +8477,14 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C452">
@@ -6350,6 +8495,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6381,6 +8531,11 @@
       </c>
     </row>
     <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6408,10 +8563,15 @@
         <v>2</v>
       </c>
       <c r="D456">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
           <t>Aquismón</t>
@@ -6425,9 +8585,14 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Armadillo de los Infante</t>
+          <t>Armadillo De Los Infante</t>
         </is>
       </c>
       <c r="C458">
@@ -6438,9 +8603,14 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Axtla de Terrazas</t>
+          <t>Axtla De Terrazas</t>
         </is>
       </c>
       <c r="C459">
@@ -6451,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -6464,6 +8639,11 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>Cerritos</t>
@@ -6477,9 +8657,14 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Cerro de San Pedro</t>
+          <t>Cerro De San Pedro</t>
         </is>
       </c>
       <c r="C462">
@@ -6490,19 +8675,29 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C463">
         <v>2</v>
       </c>
       <c r="D463">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -6516,6 +8711,11 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -6529,6 +8729,11 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
           <t>Ebano</t>
@@ -6542,6 +8747,11 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
           <t>Guadalcázar</t>
@@ -6551,10 +8761,15 @@
         <v>2</v>
       </c>
       <c r="D467">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>Huehuetlán</t>
@@ -6568,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -6577,23 +8797,33 @@
         <v>2</v>
       </c>
       <c r="D469">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Mexquitic de Carmona</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C470">
         <v>2</v>
       </c>
       <c r="D470">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -6607,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -6620,6 +8855,11 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -6633,9 +8873,14 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C474">
@@ -6646,6 +8891,11 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -6659,6 +8909,11 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>San Nicolás Tolentino</t>
@@ -6672,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Santa Catarina</t>
@@ -6685,9 +8945,14 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C478">
@@ -6698,6 +8963,11 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -6711,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -6724,6 +8999,11 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -6737,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Tamuín</t>
@@ -6750,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Tancanhuitz</t>
@@ -6763,6 +9053,11 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
           <t>Tierra Nueva</t>
@@ -6776,9 +9071,14 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Villa de Arriaga</t>
+          <t>Villa De Arriaga</t>
         </is>
       </c>
       <c r="C485">
@@ -6789,9 +9089,14 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C486">
@@ -6802,19 +9107,29 @@
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Villa de Reyes</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C487">
         <v>2</v>
       </c>
       <c r="D487">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -6828,6 +9143,11 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
           <t>Villa Juárez</t>
@@ -6841,6 +9161,11 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -6854,6 +9179,11 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -6867,6 +9197,11 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6898,6 +9233,11 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -6911,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -6924,6 +9269,11 @@
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -6933,10 +9283,15 @@
         <v>2</v>
       </c>
       <c r="D496">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6968,6 +9323,11 @@
       </c>
     </row>
     <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B499" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -6981,6 +9341,11 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
           <t>Navojoa</t>
@@ -6994,6 +9359,11 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -7007,6 +9377,11 @@
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7038,6 +9413,11 @@
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -7051,6 +9431,11 @@
       </c>
     </row>
     <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B505" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -7060,10 +9445,15 @@
         <v>2</v>
       </c>
       <c r="D505">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr">
         <is>
           <t>Cunduacán</t>
@@ -7073,10 +9463,15 @@
         <v>2</v>
       </c>
       <c r="D506">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B507" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -7090,6 +9485,11 @@
       </c>
     </row>
     <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B508" t="inlineStr">
         <is>
           <t>Jalapa</t>
@@ -7103,6 +9503,11 @@
       </c>
     </row>
     <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B509" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -7116,6 +9521,11 @@
       </c>
     </row>
     <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B510" t="inlineStr">
         <is>
           <t>Paraíso</t>
@@ -7129,6 +9539,11 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
           <t>Tacotalpa</t>
@@ -7142,6 +9557,11 @@
       </c>
     </row>
     <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr">
         <is>
           <t>Teapa</t>
@@ -7155,6 +9575,11 @@
       </c>
     </row>
     <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B513" t="inlineStr">
         <is>
           <t>Tenosique</t>
@@ -7168,6 +9593,11 @@
       </c>
     </row>
     <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B514" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7199,6 +9629,11 @@
       </c>
     </row>
     <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr">
         <is>
           <t>Aldama</t>
@@ -7208,10 +9643,15 @@
         <v>2</v>
       </c>
       <c r="D516">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B517" t="inlineStr">
         <is>
           <t>Burgos</t>
@@ -7225,6 +9665,11 @@
       </c>
     </row>
     <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B518" t="inlineStr">
         <is>
           <t>Bustamante</t>
@@ -7238,6 +9683,11 @@
       </c>
     </row>
     <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B519" t="inlineStr">
         <is>
           <t>Ciudad Madero</t>
@@ -7251,6 +9701,11 @@
       </c>
     </row>
     <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B520" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -7264,6 +9719,11 @@
       </c>
     </row>
     <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B521" t="inlineStr">
         <is>
           <t>González</t>
@@ -7277,6 +9737,11 @@
       </c>
     </row>
     <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B522" t="inlineStr">
         <is>
           <t>Mainero</t>
@@ -7290,6 +9755,11 @@
       </c>
     </row>
     <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B523" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -7303,6 +9773,11 @@
       </c>
     </row>
     <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B524" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -7316,6 +9791,11 @@
       </c>
     </row>
     <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B525" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -7329,6 +9809,11 @@
       </c>
     </row>
     <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B526" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -7342,6 +9827,11 @@
       </c>
     </row>
     <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B527" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -7355,6 +9845,11 @@
       </c>
     </row>
     <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B528" t="inlineStr">
         <is>
           <t>San Fernando</t>
@@ -7368,9 +9863,14 @@
       </c>
     </row>
     <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Soto la Marina</t>
+          <t>Soto La Marina</t>
         </is>
       </c>
       <c r="C529">
@@ -7381,6 +9881,11 @@
       </c>
     </row>
     <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B530" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -7390,10 +9895,15 @@
         <v>2</v>
       </c>
       <c r="D530">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B531" t="inlineStr">
         <is>
           <t>Tula</t>
@@ -7407,6 +9917,11 @@
       </c>
     </row>
     <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B532" t="inlineStr">
         <is>
           <t>Valle Hermoso</t>
@@ -7420,6 +9935,11 @@
       </c>
     </row>
     <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B533" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -7433,6 +9953,11 @@
       </c>
     </row>
     <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B534" t="inlineStr">
         <is>
           <t>Xicoténcatl</t>
@@ -7446,6 +9971,11 @@
       </c>
     </row>
     <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B535" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7473,10 +10003,15 @@
         <v>2</v>
       </c>
       <c r="D536">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B537" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -7490,6 +10025,11 @@
       </c>
     </row>
     <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B538" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -7499,10 +10039,15 @@
         <v>2</v>
       </c>
       <c r="D538">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B539" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -7516,9 +10061,14 @@
       </c>
     </row>
     <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Ixtacuixtla de Mariano Matamoros</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C540">
@@ -7529,6 +10079,11 @@
       </c>
     </row>
     <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B541" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -7538,10 +10093,15 @@
         <v>2</v>
       </c>
       <c r="D541">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B542" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -7555,6 +10115,11 @@
       </c>
     </row>
     <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B543" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7586,6 +10151,11 @@
       </c>
     </row>
     <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B545" t="inlineStr">
         <is>
           <t>Acayucan</t>
@@ -7599,6 +10169,11 @@
       </c>
     </row>
     <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B546" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -7608,10 +10183,15 @@
         <v>2</v>
       </c>
       <c r="D546">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B547" t="inlineStr">
         <is>
           <t>Acultzingo</t>
@@ -7625,6 +10205,11 @@
       </c>
     </row>
     <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B548" t="inlineStr">
         <is>
           <t>Alpatláhuac</t>
@@ -7638,6 +10223,11 @@
       </c>
     </row>
     <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B549" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -7651,9 +10241,14 @@
       </c>
     </row>
     <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C550">
@@ -7664,6 +10259,11 @@
       </c>
     </row>
     <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B551" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -7677,6 +10277,11 @@
       </c>
     </row>
     <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B552" t="inlineStr">
         <is>
           <t>Atoyac</t>
@@ -7690,6 +10295,11 @@
       </c>
     </row>
     <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B553" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -7703,6 +10313,11 @@
       </c>
     </row>
     <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B554" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -7716,9 +10331,14 @@
       </c>
     </row>
     <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Boca del Río</t>
+          <t>Boca Del Río</t>
         </is>
       </c>
       <c r="C555">
@@ -7729,6 +10349,11 @@
       </c>
     </row>
     <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B556" t="inlineStr">
         <is>
           <t>Calcahualco</t>
@@ -7742,6 +10367,11 @@
       </c>
     </row>
     <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B557" t="inlineStr">
         <is>
           <t>Carrillo Puerto</t>
@@ -7755,6 +10385,11 @@
       </c>
     </row>
     <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B558" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -7768,6 +10403,11 @@
       </c>
     </row>
     <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B559" t="inlineStr">
         <is>
           <t>Chinameca</t>
@@ -7781,6 +10421,11 @@
       </c>
     </row>
     <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B560" t="inlineStr">
         <is>
           <t>Chocamán</t>
@@ -7794,6 +10439,11 @@
       </c>
     </row>
     <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B561" t="inlineStr">
         <is>
           <t>Coatepec</t>
@@ -7807,6 +10457,11 @@
       </c>
     </row>
     <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B562" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -7820,6 +10475,11 @@
       </c>
     </row>
     <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B563" t="inlineStr">
         <is>
           <t>Colipa</t>
@@ -7833,6 +10493,11 @@
       </c>
     </row>
     <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B564" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -7846,9 +10511,14 @@
       </c>
     </row>
     <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C565">
@@ -7859,6 +10529,11 @@
       </c>
     </row>
     <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B566" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -7872,6 +10547,11 @@
       </c>
     </row>
     <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B567" t="inlineStr">
         <is>
           <t>Cosoleacaque</t>
@@ -7885,6 +10565,11 @@
       </c>
     </row>
     <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B568" t="inlineStr">
         <is>
           <t>Cotaxtla</t>
@@ -7898,6 +10583,11 @@
       </c>
     </row>
     <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B569" t="inlineStr">
         <is>
           <t>Coxquihui</t>
@@ -7911,6 +10601,11 @@
       </c>
     </row>
     <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B570" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -7924,6 +10619,11 @@
       </c>
     </row>
     <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B571" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -7937,6 +10637,11 @@
       </c>
     </row>
     <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B572" t="inlineStr">
         <is>
           <t>Gutiérrez Zamora</t>
@@ -7950,6 +10655,11 @@
       </c>
     </row>
     <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B573" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -7963,6 +10673,11 @@
       </c>
     </row>
     <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B574" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -7976,9 +10691,14 @@
       </c>
     </row>
     <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C575">
@@ -7989,6 +10709,11 @@
       </c>
     </row>
     <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B576" t="inlineStr">
         <is>
           <t>Ilamatlán</t>
@@ -8002,6 +10727,11 @@
       </c>
     </row>
     <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B577" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -8015,6 +10745,11 @@
       </c>
     </row>
     <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B578" t="inlineStr">
         <is>
           <t>Ixcatepec</t>
@@ -8028,6 +10763,11 @@
       </c>
     </row>
     <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B579" t="inlineStr">
         <is>
           <t>Ixtaczoquitlán</t>
@@ -8041,6 +10781,11 @@
       </c>
     </row>
     <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B580" t="inlineStr">
         <is>
           <t>Jalacingo</t>
@@ -8054,6 +10799,11 @@
       </c>
     </row>
     <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B581" t="inlineStr">
         <is>
           <t>Jáltipan</t>
@@ -8067,6 +10817,11 @@
       </c>
     </row>
     <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B582" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -8080,6 +10835,11 @@
       </c>
     </row>
     <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B583" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -8093,6 +10853,11 @@
       </c>
     </row>
     <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B584" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -8106,6 +10871,11 @@
       </c>
     </row>
     <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B585" t="inlineStr">
         <is>
           <t>Juan Rodríguez Clara</t>
@@ -8119,9 +10889,14 @@
       </c>
     </row>
     <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Juchique de Ferrer</t>
+          <t>Juchique De Ferrer</t>
         </is>
       </c>
       <c r="C586">
@@ -8132,6 +10907,11 @@
       </c>
     </row>
     <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B587" t="inlineStr">
         <is>
           <t>La Antigua</t>
@@ -8141,10 +10921,15 @@
         <v>2</v>
       </c>
       <c r="D587">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B588" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -8158,9 +10943,14 @@
       </c>
     </row>
     <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C589">
@@ -8171,6 +10961,11 @@
       </c>
     </row>
     <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B590" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -8184,6 +10979,11 @@
       </c>
     </row>
     <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B591" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -8197,6 +10997,11 @@
       </c>
     </row>
     <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B592" t="inlineStr">
         <is>
           <t>Moloacán</t>
@@ -8210,6 +11015,11 @@
       </c>
     </row>
     <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B593" t="inlineStr">
         <is>
           <t>Nautla</t>
@@ -8223,6 +11033,11 @@
       </c>
     </row>
     <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B594" t="inlineStr">
         <is>
           <t>Oluta</t>
@@ -8236,6 +11051,11 @@
       </c>
     </row>
     <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B595" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -8249,6 +11069,11 @@
       </c>
     </row>
     <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B596" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -8262,6 +11087,11 @@
       </c>
     </row>
     <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B597" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -8275,6 +11105,11 @@
       </c>
     </row>
     <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B598" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -8288,9 +11123,14 @@
       </c>
     </row>
     <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Paso de Ovejas</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C599">
@@ -8301,6 +11141,11 @@
       </c>
     </row>
     <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B600" t="inlineStr">
         <is>
           <t>Perote</t>
@@ -8314,6 +11159,11 @@
       </c>
     </row>
     <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B601" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -8327,9 +11177,14 @@
       </c>
     </row>
     <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C602">
@@ -8340,6 +11195,11 @@
       </c>
     </row>
     <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B603" t="inlineStr">
         <is>
           <t>Pueblo Viejo</t>
@@ -8353,6 +11213,11 @@
       </c>
     </row>
     <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B604" t="inlineStr">
         <is>
           <t>Puente Nacional</t>
@@ -8366,6 +11231,11 @@
       </c>
     </row>
     <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B605" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -8379,6 +11249,11 @@
       </c>
     </row>
     <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B606" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -8392,6 +11267,11 @@
       </c>
     </row>
     <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B607" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -8405,9 +11285,14 @@
       </c>
     </row>
     <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Sayula de Alemán</t>
+          <t>Sayula De Alemán</t>
         </is>
       </c>
       <c r="C608">
@@ -8418,6 +11303,11 @@
       </c>
     </row>
     <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B609" t="inlineStr">
         <is>
           <t>Sochiapa</t>
@@ -8431,9 +11321,14 @@
       </c>
     </row>
     <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C610">
@@ -8444,6 +11339,11 @@
       </c>
     </row>
     <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B611" t="inlineStr">
         <is>
           <t>Tantoyuca</t>
@@ -8453,10 +11353,15 @@
         <v>2</v>
       </c>
       <c r="D611">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B612" t="inlineStr">
         <is>
           <t>Tecolutla</t>
@@ -8470,6 +11375,11 @@
       </c>
     </row>
     <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B613" t="inlineStr">
         <is>
           <t>Tehuipango</t>
@@ -8483,6 +11393,11 @@
       </c>
     </row>
     <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B614" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -8496,6 +11411,11 @@
       </c>
     </row>
     <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B615" t="inlineStr">
         <is>
           <t>Tempoal</t>
@@ -8509,6 +11429,11 @@
       </c>
     </row>
     <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B616" t="inlineStr">
         <is>
           <t>Teocelo</t>
@@ -8522,6 +11447,11 @@
       </c>
     </row>
     <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B617" t="inlineStr">
         <is>
           <t>Texistepec</t>
@@ -8535,6 +11465,11 @@
       </c>
     </row>
     <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B618" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -8548,6 +11483,11 @@
       </c>
     </row>
     <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B619" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -8561,6 +11501,11 @@
       </c>
     </row>
     <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B620" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -8574,6 +11519,11 @@
       </c>
     </row>
     <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B621" t="inlineStr">
         <is>
           <t>Tlaltetela</t>
@@ -8583,10 +11533,15 @@
         <v>2</v>
       </c>
       <c r="D621">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B622" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -8596,10 +11551,15 @@
         <v>2</v>
       </c>
       <c r="D622">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B623" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -8613,6 +11573,11 @@
       </c>
     </row>
     <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B624" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -8626,6 +11591,11 @@
       </c>
     </row>
     <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B625" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -8639,6 +11609,11 @@
       </c>
     </row>
     <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B626" t="inlineStr">
         <is>
           <t>Uxpanapa</t>
@@ -8648,13 +11623,18 @@
         <v>2</v>
       </c>
       <c r="D626">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Vega de Alatorre</t>
+          <t>Vega De Alatorre</t>
         </is>
       </c>
       <c r="C627">
@@ -8665,6 +11645,11 @@
       </c>
     </row>
     <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B628" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -8678,6 +11663,11 @@
       </c>
     </row>
     <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B629" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -8691,6 +11681,11 @@
       </c>
     </row>
     <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B630" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -8700,10 +11695,15 @@
         <v>2</v>
       </c>
       <c r="D630">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B631" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -8717,6 +11717,11 @@
       </c>
     </row>
     <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B632" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8748,6 +11753,11 @@
       </c>
     </row>
     <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B634" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8779,6 +11789,11 @@
       </c>
     </row>
     <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B636" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -8792,6 +11807,11 @@
       </c>
     </row>
     <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B637" t="inlineStr">
         <is>
           <t>El Salvador</t>
@@ -8805,6 +11825,11 @@
       </c>
     </row>
     <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B638" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -8818,6 +11843,11 @@
       </c>
     </row>
     <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B639" t="inlineStr">
         <is>
           <t>General Pánfilo Natera</t>
@@ -8831,6 +11861,11 @@
       </c>
     </row>
     <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B640" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -8844,6 +11879,11 @@
       </c>
     </row>
     <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B641" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -8857,6 +11897,11 @@
       </c>
     </row>
     <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B642" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -8870,9 +11915,14 @@
       </c>
     </row>
     <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Noria de Ángeles</t>
+          <t>Noria De Ángeles</t>
         </is>
       </c>
       <c r="C643">
@@ -8883,6 +11933,11 @@
       </c>
     </row>
     <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B644" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -8896,6 +11951,11 @@
       </c>
     </row>
     <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B645" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -8909,6 +11969,11 @@
       </c>
     </row>
     <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B646" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -8922,6 +11987,11 @@
       </c>
     </row>
     <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B647" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -8935,6 +12005,11 @@
       </c>
     </row>
     <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B648" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -8948,6 +12023,11 @@
       </c>
     </row>
     <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B649" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -8961,19 +12041,29 @@
       </c>
     </row>
     <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C650">
         <v>2</v>
       </c>
       <c r="D650">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B651" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -8987,6 +12077,11 @@
       </c>
     </row>
     <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B652" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -9000,6 +12095,11 @@
       </c>
     </row>
     <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B653" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -9013,6 +12113,11 @@
       </c>
     </row>
     <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B654" t="inlineStr">
         <is>
           <t>Total</t>
@@ -9036,41 +12141,6 @@
       </c>
       <c r="D655">
         <v>1</v>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 814,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>Marzo de 2017</t>
-        </is>
       </c>
     </row>
   </sheetData>
